--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_02_Full_121_Cau/Day_02_Ngan_Hang_Phan_01_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_02_Full_121_Cau/Day_02_Ngan_Hang_Phan_01_21_Cau.xlsx
@@ -729,7 +729,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách phát biểu có số liệu hoặc nhật ký (log) khỏi phát biểu suy đoán nguyên nhân hay giải pháp.</t>
+          <t>Dữ liệu log 37/50 hồ sơ phải nhập lại địa chỉ với trung vị 4 phút trực tiếp hỗ trợ: Điểm đau nằm ở việc nhập lại địa chỉ (a), Có 37 hồ sơ bị nhập lại trong mẫu (b), và Việc nhập lại làm tăng thời gian xử lý của nhân viên (d). Ý kiến về biểu mẫu (c) là suy đoán chủ quan.</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Quick win phải đồng thời có tác động đáng kể và nỗ lực tương đối thấp.</t>
+          <t>Quick win được định nghĩa là cơ hội có tác động đáng kể với nỗ lực tương đối thấp. Cơ hội B có tác động 4 (cao) và nỗ lực 2 (thấp), là quick win rõ ràng hơn Cơ hội A (tác động 5 nhưng nỗ lực 5) và C (tác động chỉ 2).</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_02_Full_121_Cau/Day_02_Ngan_Hang_Phan_01_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_02_Full_121_Cau/Day_02_Ngan_Hang_Phan_01_21_Cau.xlsx
@@ -670,10 +670,18 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Viết câu hỏi về người, bước và kết quả trước; chỉ sau đó mới liệt kê điều chưa biết.
-Phân tích theo nguyên lý thiết kế: Viết câu hỏi về người, bước và kết quả trước; chỉ sau đó mới liệt kê điều chưa biết.</t>
+- Câu hỏi khám phá vấn đề đủ 4 yếu tố (1.5 điểm): Xác định rõ người thực hiện, quy trình, điểm đau cụ thể và kết quả mong muốn đo lường được.
+- Hai giả định kiểm chứng then chốt (1.5 điểm): Nêu đúng giả định về chất lượng dữ liệu lịch nguồn và giả định về giải pháp phần mềm tất định đơn giản (phi AI).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+- Viết lại thành câu hỏi khám phá vấn đề (Problem Discovery Question):
+"Làm thế nào để [nhân viên và quản lý các phòng ban - Người thực hiện] có thể [tìm khung giờ trống phù hợp và thống nhất lịch họp liên phòng ban - Quy trình] mà không gặp phải [tình trạng xung đột lịch, tốn 20-30 phút gửi email qua lại trao đổi qua nhiều kênh - Điểm đau], nhằm đạt được [việc chốt lịch họp nhanh chóng dưới 2 phút với tỷ lệ tham dự đúng giờ trên 90% - Kết quả mong muốn]?"
+- Hai giả định phải kiểm chứng trước khi chọn giải pháp AI:
+1. Giả định về dữ liệu nguồn: Lịch cá nhân trên Google Calendar / Outlook của nhân viên đã được cập nhật chính xác và đầy đủ các khung giờ bận thực tế hay chưa? (Nếu dữ liệu lịch rác hoặc không được cập nhật, AI cũng sẽ xếp lịch sai).
+2. Giả định về giải pháp phi AI: Liệu một công cụ xếp lịch tất định truyền thống (như Calendly, Doodle, hoặc thuật toán tìm khoảng trống giao nhau trong API lịch) đã đủ giải quyết 80% vấn đề mà không cần đến sự phức tạp và chi phí của LLM hay không?
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Phương pháp 'Problem-First Thinking' (tư duy xuất phát từ vấn đề) cảnh báo bẫy 'Solution-in-search-of-a-problem' (có búa AI đi tìm đinh). Trước khi quyết định đầu tư tác nhân AI, người làm sản phẩm phải định hình rõ ràng tác nhân, quy trình, điểm ma sát đo đếm được và kiểm định tính khả thi của các phương án kỹ thuật đơn giản hơn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Torres, T. (2021). Continuous Discovery Habits. Product Talk LLC (https://www.producttalk.org/); Harvard Business Review - Stop the Meeting Madness (https://hbr.org/2017/07/stop-the-meeting-madness)</t>
         </is>
       </c>
     </row>
@@ -764,10 +772,20 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đánh dấu từng chi tiết là quan sát được hay chỉ là suy luận.
-Phân tích theo nguyên lý thiết kế: Đánh dấu từng chi tiết là quan sát được hay chỉ là suy luận.</t>
+- Xác định đúng người thực hiện và bước quy trình (1.0 điểm): Nêu rõ kế toán/quản lý và các bước nhập liệu/kiểm tra.
+- Chỉ ra điểm đau và bằng chứng định lượng (1.0 điểm): Nêu đúng tỷ lệ lỗi 30% (6/20 hóa đơn) và thời gian sửa 12 phút/hóa đơn.
+- Phân định giả định chưa kiểm chứng (1.0 điểm): Nhận diện đúng giả định ngầm định về nguyên nhân lỗi gõ tay thay vì lỗi do định dạng tài liệu.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Phân tích dữ liệu quan sát quy trình kế toán:
+- Người thực hiện (Actors): Nhân viên kế toán (tiếp nhận hóa đơn và nhập liệu), Quản lý kế toán (kiểm tra phê duyệt và trả lại hóa đơn sai).
+- Bước trong quy trình (Workflow step): Bước 2 (Kế toán sao chép số tiền thủ công từ PDF vào bảng tính) và Bước 3 (Quản lý phát hiện sai sót và trả lại hồ sơ).
+- Điểm đau (Pain point): Tỷ lệ nhập liệu sai số tiền cao dẫn đến việc hóa đơn bị từ chối phê duyệt, phát sinh lãng phí thời gian sửa chữa và làm chậm trễ chu kỳ thanh toán cho nhà cung cấp.
+- Bằng chứng thực nghiệm quan sát được (Empirical evidence): 6/20 hóa đơn bị trả lại vì sai số tiền (tỷ lệ lỗi 30%); mỗi lượt sửa chữa tiêu tốn trung bình 12 phút (tổng lãng phí 72 phút cho 20 hóa đơn).
+- Một điều vẫn chỉ là giả định (Unverified assumption): Giả định rằng nguyên nhân sai sót là do kế toán gõ nhầm bất cẩn. Thực tế có thể do file PDF chất lượng kém, bản scan mờ, cấu trúc bảng phức tạp, hoặc cách thể hiện định dạng số (dấu chấm phân tách phần nghìn vs dấu phẩy thập phân) gây hiểu nhầm.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Trong thiết kế trải nghiệm người dùng (UX Research &amp; Workflow Mapping), việc phân biệt rạch ròi giữa 'Dữ kiện quan sát được' (Fact/Evidence) và 'Suy đoán nguyên nhân' (Hypothesis) là tối quan trọng để tránh đưa ra các giải pháp tự động hóa lệch đích.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Nielsen Norman Group - Workflow Mapping &amp; Usability Testing (https://www.nngroup.com/articles/workflow-testing/); Dumas, J. S., &amp; Redish, J. (1999). A Practical Guide to Usability Testing.</t>
         </is>
       </c>
     </row>
@@ -803,10 +821,18 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu bằng một sự cố cụ thể rồi đi dần tới tác động và quyết định.
-Phân tích theo nguyên lý thiết kế: Bắt đầu bằng một sự cố cụ thể rồi đi dần tới tác động và quyết định.</t>
+- Câu 1 &amp; 2 về sự cố và quy trình bàn giao (1.5 điểm): Hỏi đúng sự cố cụ thể gần nhất và luồng bàn giao công việc giữa vận hành - bảo trì.
+- Câu 3 &amp; 4 về tác động, người chịu trách nhiệm và tiêu chí thành công (1.5 điểm): Khai thác đúng tần suất/thiệt hại và xác định rõ owner cùng bằng chứng thành công mà không gợi ý giải pháp AI.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Bốn câu hỏi khám phá vấn đề (Discovery Questions) không gợi ý giải pháp:
+1. Khám phá sự cố gần đây: "Anh/chị có thể chia sẻ chi tiết về lần gần đây nhất một máy móc bị hỏng bất ngờ diễn ra như thế nào, máy thuộc dây chuyền nào và triệu chứng ban đầu là gì?"
+2. Khám phá quy trình và điểm bàn giao: "Khi phát hiện máy có dấu hiệu bất thường, kỹ thuật viên vận hành thông báo cho đội bảo trì bằng cách nào, và các bước bàn giao hiện trường diễn ra theo quy trình nào?"
+3. Khám phá tần suất, tác động và rủi ro: "Trung bình mỗi tháng có bao nhiêu sự cố dừng máy đột xuất, mỗi lần dừng máy gây gián đoạn sản xuất bao lâu và ước tính thiệt hại kinh tế là bao nhiêu?"
+4. Khám phá người chịu trách nhiệm và bằng chứng thành công: "Ai là người chịu trách nhiệm cuối cùng về chỉ số sẵn sàng của thiết bị (OEE/Uptime), và nếu vấn đề dừng máy được cải thiện thì số liệu cụ thể nào sẽ chứng minh dự án thành công?"
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Kỹ năng phỏng vấn khám phá bên liên quan (Stakeholder Discovery) tuân thủ nguyên tắc 'Problem Space over Solution Space'. Thay vì thảo luận về thuật toán Machine Learning hay cảm biến IoT, người làm sản phẩm tập trung đào sâu sự cố thực tế, tổn thất kinh tế và thước đo thành công nghiệp vụ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Fitzpatrick, R. (2013). The Mom Test. Robfitz Ltd (http://momtestbook.com/); Teresa Torres - Continuous Discovery Habits (https://www.producttalk.org/)</t>
         </is>
       </c>
     </row>
@@ -842,10 +868,22 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đừng biến đề xuất AI thành kết luận; hãy truy ngược từ số liệu đến khâu gây ra và người chịu trách nhiệm.
-Phân tích theo nguyên lý thiết kế: Đừng biến đề xuất AI thành kết luận; hãy truy ngược từ số liệu đến khâu gây ra và người chịu trách nhiệm.</t>
+- Tách bạch dữ kiện và giả định (1.0 điểm): Liệt kê đủ 3 dữ kiện quan sát và 2 giả định ngầm định chưa kiểm chứng.
+- Đặt 3 câu hỏi khám phá sâu (1.0 điểm): Hỏi đúng về nút thắt thời gian, hậu quả chậm trễ và người có quyền quyết định.
+- Nêu ngưỡng bằng chứng định lượng (1.0 điểm): Đưa ra chỉ số định lượng cụ thể (tỷ lệ thời gian tìm kiếm, cỡ mẫu hợp đồng) cần xác minh trước khi chọn giải pháp.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tách biệt dữ kiện đã có khỏi giả định còn thiếu bằng chứng:
+- Dữ kiện đã có (Facts): (1) 4/10 hợp đồng phải hỏi lại điều khoản thanh toán (tỷ lệ 40%); (2) Nhân viên pháp chế mất trung vị 25 phút để tra cứu; (3) Chưa có số liệu phân rã thời gian giữa khâu tìm kiếm và khâu phê duyệt.
+- Giả định thiếu bằng chứng (Assumptions): (1) Giả định việc đọc hiểu hợp đồng là nút thắt chính gây chậm trễ (thay vì do mẫu hợp đồng thiếu chuẩn hóa hoặc đối tác cố tình kéo dài đàm phán); (2) Giả định việc đưa AI vào đọc hợp đồng sẽ giảm được thời gian tra cứu và giải quyết được tận gốc nguyên nhân phải hỏi lại.
+2. Ba câu hỏi tiếp theo để phân biệt nút thắt, hậu quả và quyền quyết định:
+- Phân biệt nút thắt: "Trong 25 phút tra cứu của pháp chế, thời gian lật tìm trang tài liệu chiếm bao nhiêu phút so với thời gian đối chiếu quy định pháp luật và chính sách tín dụng nội bộ?"
+- Đánh giá hậu quả: "Việc 4/10 hợp đồng phải hỏi lại điều khoản gây chậm tiến độ ký kết trung bình bao nhiêu ngày, và có dẫn đến khiếu nại hoặc mất hợp đồng không?"
+- Xác định quyền quyết định: "Ai là người có thẩm quyền phê duyệt cuối cùng để chấp nhận ngoại lệ thanh toán hoặc chuẩn hóa lại mẫu hợp đồng?"
+3. Ngưỡng bằng chứng cần đạt trước khi đánh giá giải pháp: Phải có dữ liệu đo lường thời gian phân rã chứng minh khâu tìm kiếm thủ công chiếm &gt; 60% tổng thời gian (tối thiểu 15 phút) trên cỡ mẫu từ 50 hợp đồng trở lên.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Đề xuất 'Dùng AI đọc hợp đồng' thường là phản xạ vội vàng trước các triệu chứng bề mặt. Bằng cách thiết lập ngưỡng bằng chứng định lượng (Evidence Threshold) và phân tách nút thắt quy trình, đội ngũ sản phẩm tránh lãng phí nguồn lực vào các giải pháp đắt đỏ không trúng đích.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Cagan, M. (2017). Inspired: How to Create Tech Products Customers Love. Wiley (https://www.svpg.com/books/inspired/); Teresa Torres - Continuous Discovery Habits (https://www.producttalk.org/)</t>
         </is>
       </c>
     </row>
@@ -976,10 +1014,22 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách 'cách đang làm' khỏi 'điều không được vi phạm'.
-Phân tích theo nguyên lý thiết kế: Tách 'cách đang làm' khỏi 'điều không được vi phạm'.</t>
+- Phân rã nguyên tắc nền tảng (1.5 điểm): Phân biệt rõ nhu cầu giải đáp tức thì với ràng buộc pháp lý của khiếu nại tài chính, bác bỏ tư duy sao chép đối thủ.
+- Đề xuất phương án tiếp cận phân tầng (1.5 điểm): Thiết kế giải pháp kết hợp AI tự động giải đáp 24/7 cho câu hỏi chuẩn và thu thập ticket có cấu trúc để người có thẩm quyền duyệt.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Phân rã bài toán theo nguyên tắc nền tảng (First Principles Problem Decomposition):
+1. Bóc tách bản chất nhu cầu và các ràng buộc cốt lõi:
+- Giả định sai lầm hiện tại: 'Dịch vụ hỗ trợ bắt buộc phải có con người trực tổng đài 24/7' chỉ vì đối thủ làm như vậy (tư duy bắt chước theo quy ước cũ).
+- Nhu cầu cơ bản thật sự của khách hàng: Khi gặp thắc mắc vào ban đêm, khách hàng cần nhận được câu trả lời chính xác, tức thì cho các vấn đề thông thường; và khi gặp sự cố tài chính, họ cần sự an tâm rằng yêu cầu đã được tiếp nhận an toàn và sẽ được xử lý đúng cam kết.
+- Ràng buộc pháp lý và an toàn bất biến: Khiếu nại tài chính (liên quan đến hoàn tiền, bồi thường, rủi ro gian lận) bắt buộc phải do nhân sự có thẩm quyền phê duyệt, không thể giao toàn quyền cho AI hay nhân viên trực ca đêm không đủ thẩm quyền.
+2. Đề xuất phương án tiếp cận mới:
+- Xây dựng hệ thống Hỗ trợ Đa tầng Phân cấp (Tiered Support Architecture):
++ Tầng 1 (Tự động 24/7): Triển khai AI Chatbot/RAG tra cứu trực tiếp từ tài liệu chuẩn để giải đáp 100% câu hỏi phổ biến tức thì cho khách hàng mọi lúc.
++ Tầng 2 (Thu thập có cấu trúc cho sự cố tài chính): Đối với khiếu nại tài chính phát sinh ngoài giờ, bot hướng dẫn khách hàng cung cấp chứng từ có cấu trúc (ticket) và gửi email xác nhận đã ghi nhận an toàn, cam kết nhân sự có thẩm quyền sẽ liên hệ xử lý trong 2 giờ đầu của ngày làm việc tiếp theo.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Tư duy First Principles đòi hỏi đập vỡ các hình thức vận hành truyền thống ('phải có người trực 24/7') để trở về các chân lý nền tảng: nhu cầu thông tin tức thì và ràng buộc phê duyệt tài chính. Giải pháp phân tầng giúp giảm 70% chi phí nhân sự mà vẫn đảm bảo 100% tính tuân thủ pháp lý.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Aristotelian First Principles in Systems Design; Porter, M. E. (1996). What Is Strategy? Harvard Business Review (https://hbr.org/1996/11/what-is-strategy)</t>
         </is>
       </c>
     </row>
@@ -1013,10 +1063,24 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Xác định kết quả cần đạt (outcome) trước khi giữ lại bất kỳ định dạng nào.
-Phân tích theo nguyên lý thiết kế: Xác định kết quả cần đạt (outcome) trước khi giữ lại bất kỳ định dạng nào.</t>
+- Nhận diện đúng giả định ẩn (1.0 điểm): Chỉ ra việc ngộ nhận lãnh đạo cần đọc hết 20 trang PDF để nắm bắt KPI.
+- Nêu đủ các ràng buộc thật sự (1.0 điểm): Liệt kê đúng ràng buộc thời gian (trước thứ Hai), dữ liệu có cấu trúc và khả năng truy vết kiểm toán.
+- Thiết kế quy trình mới tinh gọn (1.0 điểm): Đề xuất Dashboard/Tóm tắt ngoại lệ 1 trang tự động có deep link truy vết dữ liệu gốc.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chỉ ra giả định ẩn (Hidden Assumption):
+Giả định sai lầm là: Lãnh đạo cần và sẽ đọc hết một tài liệu PDF dài 20 trang để nắm bắt tình hình hoạt động; định dạng PDF 20 trang được coi là biểu hiện của sự kỹ lưỡng, trong khi thực tế lãnh đạo bị quá tải thông tin và không thể phát hiện sớm các bất thường.
+2. Các ràng buộc thật sự (True Constraints):
+- Ràng buộc thời gian: Lãnh đạo phải phát hiện được độ lệch KPI trước thời điểm giao ban sáng thứ Hai.
+- Ràng buộc dữ liệu: Dữ liệu nguồn đã có cấu trúc trong cơ sở dữ liệu/kho dữ liệu.
+- Ràng buộc kiểm toán: Mọi quyết định rủi ro cao dựa trên số liệu báo cáo bắt buộc phải có khả năng truy vết nguồn gốc (audit trail) về từng bản ghi dữ liệu gốc.
+3. Phương án dựng lại quy trình (Re-engineered Workflow):
+- Thay thế file PDF 20 trang bằng Bảng điều khiển KPI tự động (Live Dashboard) kết hợp Báo cáo Tóm tắt Điều hành (Executive Exception Summary) 1 trang gửi qua email/Slack vào 7h sáng thứ Hai.
+- Hệ thống sử dụng quy tắc và thuật toán phát hiện bất thường (Anomaly Detection) để chỉ làm nổi bật các chỉ số bị lệch ngưỡng cho phép (Exception-based Reporting).
+- Mỗi chỉ số lệch chuẩn đều đính kèm một đường link định danh (deep link) cho phép lãnh đạo nhấp vào để kiểm tra dữ liệu nguồn và lịch sử phê duyệt khi cần ra quyết định.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên tắc 'Management by Exception' kết hợp First Principles loại bỏ hoàn toàn các 'tài liệu rác' (wasteful artifacts). Chuyển đổi từ tài liệu tĩnh 20 trang sang báo cáo ngoại lệ theo thời gian thực giải phóng thời gian cho đội ngũ và tăng tốc độ phản ứng của ban giám đốc.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Drucker, P. F. (1954). The Practice of Management; Martin Fowler - Information Dashboards &amp; Continuous Delivery (https://martinfowler.com/articles/patterns-of-distributed-systems/)</t>
         </is>
       </c>
     </row>
@@ -1198,10 +1262,19 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tìm ô nào có bằng chứng yếu nhất và hỏi phép đo nào sẽ thay đổi vị trí của nó.
-Phân tích theo nguyên lý thiết kế: Tìm ô nào có bằng chứng yếu nhất và hỏi phép đo nào sẽ thay đổi vị trí của nó.</t>
+- Giải thích quyết định chọn X (1.5 điểm): Nêu rõ việc chọn X vì tỷ lệ Impact/Effort lý thuyết vượt trội (Quick Win 5/2 vs 4/3).
+- Đề xuất phép kiểm chứng và kịch bản đảo thứ hạng (1.5 điểm): Nêu phép đo spike/phân tích mẫu thực tế để chứng minh sự mong manh của phỏng đoán, chỉ ra khi nỗ lực tăng hoặc tác động giảm thì Y sẽ vượt lên.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Giải thích quyết định tạm thời của nhóm:
+Nhóm chọn cơ hội X dựa trên ma trận Impact-Effort truyền thống vì trên lý thuyết điểm số, X có tỷ suất lợi ích trên chi phí vượt trội (Tỷ lệ Impact/Effort = 5/2 = 2,5 so với Y là 4/3 = 1,33). X rơi vào góc phần tư 'Quick Win' (tác động tối đa với nỗ lực tối thiểu), tạo sức hút lớn cho các quyết định ngắn hạn.
+2. Phép kiểm chứng tối thiểu có thể làm đảo lộn thứ hạng:
+- Điểm yếu cốt tử của X là ước lượng hoàn toàn dựa trên phỏng đoán cảm tính (conjecture), trong khi Y được bảo chứng bởi dữ liệu nhật ký (log) thực tế 3 tháng.
+- Phép kiểm chứng tối thiểu: Thực hiện một thử nghiệm dò đường kỹ thuật (Technical Spike / Prototype) kéo dài 2-3 ngày để thử nghiệm trích xuất dữ liệu thực tế cho X, đồng thời phân tích 100 trường hợp người dùng gần nhất.
+- Kịch bản làm đảo thứ hạng: Nếu phép kiểm chứng phát hiện dữ liệu cho X bị thiếu cấu trúc, tỷ lệ ngoại lệ cao khiến Nỗ lực thực tế nhảy từ 2 lên 5 (Effort = 5), hoặc nhu cầu thực tế của người dùng thấp khiến Tác động giảm từ 5 xuống 2 (Impact = 2), tỷ lệ của X sẽ tụt xuống dưới Y (2/5 = 0,4 &lt; 1,33). Khi đó Y sẽ được chọn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Trong khung ưu tiên sản phẩm (RICE, Impact-Effort), chỉ số 'Độ tin cậy' (Confidence Score) là nhân tố quyết định. Một ước lượng Impact 5 nhưng Confidence 20% luôn có rủi ro cao hơn nhiều so với Impact 4 nhưng Confidence 90% từ log thực nghiệm.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Intercom - RICE: Simple prioritization for product managers (https://www.intercom.com/blog/rice-simple-prioritization-for-product-managers/); Cagan, M. (2017). Inspired.</t>
         </is>
       </c>
     </row>
@@ -1233,10 +1306,23 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: So chất lượng nguồn của từng nhận định trước khi so độ lớn.
-Phân tích theo nguyên lý thiết kế: So chất lượng nguồn của từng nhận định trước khi so độ lớn.</t>
+- Lập danh sách ngắn chuẩn xác (1.0 điểm): Xếp thứ tự A (ưu tiên 1), C (ưu tiên 2), B (loại/chưa chọn).
+- Phân tích bằng chứng và điều chưa chắc chắn của A và C (1.0 điểm): Nêu rõ bằng chứng 28 ticket của A và rủi ro tuân thủ/tranh chấp owner của C.
+- Lý do loại bài toán B (1.0 điểm): Phân tích con số 500 giờ của B chỉ là suy đoán thiếu log và thiếu actor cụ thể.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Tạo danh sách ngắn ưu tiên bài toán ứng viên có đối chiếu bằng chứng:
+- Danh sách ngắn ưu tiên:
+1. Ưu tiên số 1: Bài toán A.
+2. Ưu tiên số 2: Bài toán C.
+3. Loại bỏ / Chưa chọn: Bài toán B.
+- Phân tích chi tiết từng bài toán:
++ Bài toán A: Bằng chứng mạnh với 28 ticket thực tế cùng chung điểm đau, tác nhân và quy trình đều đã được xác định rõ ràng. Điều chưa chắc chắn: Chưa đo lường quy mô hậu quả tài chính. Điểm bất đồng: Không có. Lý do chọn: Bằng chứng thực nghiệm cao nhất, có thể định lượng tài chính nhanh chóng qua phỏng vấn 28 ca.
++ Bài toán C: Bằng chứng gồm 9 trường hợp có quy trình rõ, hậu quả tuân thủ pháp lý cao. Điều chưa chắc chắn: Cỡ mẫu nhỏ (9 ca). Điểm bất đồng: Tranh chấp về người chịu trách nhiệm chính (ownership). Lý do xếp sau A: Cần giải quyết dứt điểm quyền sở hữu và thẩm quyền trước khi bắt tay xây dựng giải pháp.
++ Bài toán B: Bằng chứng gần như bằng 0 (chỉ là con số ước tính cảm tính 500 giờ từ stakeholder, không có log chứng minh, không có người thực hiện cụ thể). Lý do loại/chưa chọn: Vi phạm nguyên tắc ra quyết định dựa trên bằng chứng; nguy cơ cao là giải quyết một bài toán ảo.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Ưu tiên hóa vấn đề phải dựa trên thứ bậc độ tin cậy của bằng chứng (Hierarchy of Evidence): Nhật ký/Ticket thực tế (Empirical Behavior) &gt; Ý kiến phỏng đoán của Stakeholder (Opinion/Conjecture). Đầu tư vào bài toán thiếu owner hoặc thiếu dữ liệu sẽ dẫn đến dự án bị đình trệ khi chuyển giao.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Teresa Torres - Opportunity Solution Tree (https://www.producttalk.org/opportunity-solution-tree/); Cagan, M. (2020). Empowered. Wiley (https://www.svpg.com/books/empowered/)</t>
         </is>
       </c>
     </row>
@@ -1267,10 +1353,21 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: So từng thẻ trên cùng các trường, không so điểm mạnh của thẻ này với điểm yếu khác loại của thẻ kia.
-Phân tích theo nguyên lý thiết kế: So từng thẻ trên cùng các trường, không so điểm mạnh của thẻ này với điểm yếu khác loại của thẻ kia.</t>
+- Chọn đúng Thẻ A và nêu lý do (1.0 điểm): Chọn Thẻ A vì có actor rõ ràng và 12 ticket minh chứng thực tế.
+- Chỉ ra điều chưa chắc chắn của Thẻ A (1.0 điểm): Nêu rõ tác động tài chính/thời gian tổng thể chưa được định lượng nhưng kiểm chứng được.
+- Phân tích lý do bác bỏ Thẻ B (1.0 điểm): Chỉ ra Thẻ B thiếu cả actor và workflow, con số 200 giờ là suy đoán vô căn cứ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+- Quyết định chọn bài toán tạm thời: Chọn THẺ A.
+- Lý do lựa chọn Thẻ A:
+Thẻ A có bằng chứng thực nghiệm rõ ràng từ người dùng thực (12 phiếu hỗ trợ xác thực) và tác nhân thực hiện (actor) đã được xác định cụ thể. Điều này khẳng định vấn đề có thật trong vận hành hàng ngày, tác nhân có thể tiếp cận ngay để phỏng vấn sâu và khảo sát quy trình.
+- Điều chưa chắc chắn (Uncertainty) của Thẻ A:
+Tổng tác động định lượng (tổng số giờ lãng phí, chi phí tài chính phát sinh) chưa được đo lường chính xác. Tuy nhiên, điều chưa chắc chắn này có thể được kiểm chứng nhanh chóng bằng cách phỏng vấn 12 người đã gửi phiếu hỗ trợ để đo thời gian tiêu tốn trung bình cho mỗi phiếu.
+- Lý do chưa chọn Thẻ B:
+Con số 'tiết kiệm 200 giờ' của Thẻ B là một chỉ số ảo (phantom metric) hoàn toàn thiếu căn cứ khi chưa xác định được tác nhân (ai làm?) và quy trình (diễn ra ở bước nào?). Khi không có tác nhân và quy trình cụ thể, đội ngũ không thể tiến hành quan sát thực địa và có nguy cơ cao xây dựng giải pháp cho một vấn đề không tồn tại trong thực tế.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Tiêu chí cốt lõi của một bài toán sản phẩm hợp lệ là tính có thể kiểm chứng được (Verifiability). Vấn đề có Actor và Evidence dù chưa đo được Impact vẫn có giá trị hơn rất nhiều so với một lời hứa hẹn Impact khổng lồ nhưng không gắn với bất kỳ con người hay quy trình nghiệp vụ cụ thể nào.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Torres, T. (2021). Continuous Discovery Habits (https://www.producttalk.org/); Bland, D. J., &amp; Osterwalder, A. (2019). Testing Business Ideas. Wiley (https://www.strategyzer.com/library/testing-business-ideas)</t>
         </is>
       </c>
     </row>
@@ -1349,10 +1446,18 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Hỏi điều gì phân biệt hai nhóm và dữ liệu nào kiểm tra được điều đó.
-Phân tích theo nguyên lý thiết kế: Hỏi điều gì phân biệt hai nhóm và dữ liệu nào kiểm tra được điều đó.</t>
+- Kết luận kiểm chứng cân bằng khách quan (1.5 điểm): Nhận diện đúng sự phân hóa giữa 2 nhóm, quy trình đã có cách làm nhanh (dưới 3 phút nhờ mẫu) nên không phải nút thắt hệ thống.
+- Sửa lại bài toán ứng viên chuẩn xác (1.5 điểm): Chuyển trọng tâm từ tự động hóa AI toàn bộ sang chuẩn hóa và phổ biến biểu mẫu có sẵn để đưa thời gian về dưới 3 phút.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Kết luận kiểm chứng cân bằng (Balanced Validation Finding):
+Vấn đề thời gian duyệt nghỉ phép kéo dài KHÔNG PHẢI là vấn đề hệ thống mang tính phổ quát đối với mọi nhân viên, mà là sự phân hóa hành vi rõ rệt giữa hai nhóm: nhóm gặp khó khăn (3/5 người mất trên 20 phút) do không tiếp cận được công cụ chuẩn, và nhóm tối ưu (2/5 người chỉ mất dưới 3 phút nhờ sử dụng biểu mẫu có sẵn). Điều này chứng minh bản thân quy trình đã có giải pháp nhanh hiệu quả, điểm nghẽn nằm ở khâu nhận thức, đào tạo và sự sẵn có của biểu mẫu chuẩn hóa.
+2. Sửa lại bài toán ứng viên (Reframed Candidate Problem):
+- Đề bài ban đầu chưa sửa: 'Ứng dụng AI để tự động hóa toàn bộ quy trình xin nghỉ phép'.
+- Bài toán đã sửa chuẩn xác: 'Làm thế nào để chuẩn hóa và đưa biểu mẫu nghỉ phép có sẵn tích hợp trực tiếp vào giao diện làm việc hàng ngày của 100% nhân viên, kết hợp tự động điền sẵn thông tin cá nhân cơ bản để giảm thời gian tạo đơn của nhóm 3 người từ trên 20 phút xuống dưới 3 phút như nhóm sử dụng mẫu?'
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Khám phá nhanh (Rapid Validation) giúp ngăn ngừa việc phức tạp hóa vấn đề bằng AI. Khi một bộ phận người dùng đã thực hiện công việc cực nhanh nhờ công cụ đơn giản (mẫu sẵn), giải pháp đúng đắn là nhân rộng mẫu chuẩn thay vì đầu tư một hệ thống tự động hóa cồng kềnh.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Bland, D. J., &amp; Osterwalder, A. (2019). Testing Business Ideas. Wiley (https://www.strategyzer.com/library/testing-business-ideas); Nielsen Norman Group - Discovery Phase (https://www.nngroup.com/articles/discovery-phase/)</t>
         </is>
       </c>
     </row>
@@ -1388,10 +1493,24 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Vẽ các bước được tài liệu nói tới rồi đánh dấu chỗ trống.
-Phân tích theo nguyên lý thiết kế: Vẽ các bước được tài liệu nói tới rồi đánh dấu chỗ trống.</t>
+- Phạm vi đã chứng minh (1.0 điểm): Nêu rõ luồng trích xuất mã, gọi API tra cứu và sinh bản nháp trả lời email.
+- Khoảng trống và rủi ro trọng yếu (1.0 điểm): Chỉ ra thiếu xử lý lỗi API, rủi ro khi đổi địa chỉ và thiếu khâu phê duyệt trước khi gửi.
+- Bài học tái sử dụng cụ thể (1.0 điểm): Đề xuất tái sử dụng phần trích xuất nháp và bổ sung fallback khi lỗi API cùng giao diện duyệt human-in-the-loop.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Ghi chú nghiên cứu giải pháp hiện có (Solution Gap Analysis):
+1. Phạm vi quy trình đã được chứng minh (Demonstrated Scope):
+- Luồng chuẩn thuận lợi (Happy Path): Tự động tiếp nhận email -&gt; Sử dụng mô hình ngôn ngữ để trích xuất mã vận đơn/đơn hàng -&gt; Gọi API truy vấn trạng thái đơn -&gt; Tự động soạn thảo email trả lời khách hàng dưới dạng bản nháp.
+2. Khoảng trống quy trình và rủi ro vận hành (Gaps &amp; Risks):
+- Khoảng trống xử lý lỗi hệ thống (Fault Tolerance Gap): Không có kịch bản xử lý khi API tra cứu bị timeout, trả mã lỗi 500 hoặc đơn hàng không tồn tại, có thể khiến bot sinh ảo giác xin lỗi sai lệch.
+- Rủi ro bảo mật và toàn vẹn dữ liệu: Không xử lý yêu cầu thay đổi địa chỉ giao hàng (yêu cầu nhạy cảm liên quan đến gian lận chuyển hướng đơn) do thiếu xác thực danh tính chủ tài khoản.
+- Rủi ro giao tiếp: Thiếu bước phê duyệt của con người (Human-in-the-loop review) trước khi gửi thư, dẫn đến nguy cơ gửi thông tin sai lệch trực tiếp tới khách hàng.
+3. Bài học có thể tái sử dụng cho thiết kế mới (Reusable Lessons):
+- Kế thừa khả năng trích xuất thực thể (NER) và soạn nháp tự động từ email.
+- Bắt buộc phải bổ sung: (1) Cơ chế Retry và Fallback an toàn khi API lỗi; (2) Cơ chế xác thực OTP/chuyển tiếp nhân viên cho các tác vụ thay đổi thông tin đơn hàng; (3) Giao diện 'Một cú nhấp chuột' (One-click approval) để tư vấn viên kiểm duyệt nháp trước khi phát đi.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Phân tích khoảng trống giải pháp (Solution Gap Research) giúp kế thừa những thành phần đã được chứng minh hiệu quả trong khi chủ động nhận diện và bọc lót các điểm mù kiến trúc (Edge Cases, API Failures, State Mutation Risks) trước khi đưa vào sản xuất.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google Cloud Architecture Center - Patterns for Resilient AI Architectures (https://cloud.google.com/architecture); Nygard, M. T. (2018). Release It!. Pragmatic Bookshelf (https://pragprog.com/titles/mnee2/release-it-second-edition/)</t>
         </is>
       </c>
     </row>
@@ -1425,10 +1544,23 @@
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Viết bốn dòng: bước có bằng chứng, bước thiếu, hậu quả và bài học.
-Phân tích theo nguyên lý thiết kế: Viết bốn dòng: bước có bằng chứng, bước thiếu, hậu quả và bài học.</t>
+- Xác định đúng phạm vi đã chứng minh (1.0 điểm): Nêu rõ chỉ mới phân loại ticket và đề xuất bản nháp (mức hỗ trợ/copilot).
+- Chỉ ra khoảng trống và rủi ro tiếp thị quá đà (1.0 điểm): Nhận diện việc thiếu hành động/escalation/đo lỗi và rủi ro uy tín nếu tự động hóa toàn bộ.
+- Đưa ra bài học ứng dụng đúng mức (1.0 điểm): Khuyến nghị chỉ áp dụng ở vai trò copilot/hỗ trợ nhân viên, không bật chế độ tự hành gửi tin trực tiếp.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Ghi chú nghiên cứu và thẩm định giải pháp nhà cung cấp:
+1. Phạm vi đã được chứng minh (Demonstrated Scope):
+Hệ thống của nhà cung cấp chỉ mới chứng minh được khả năng Hỗ trợ nhận thức (Cognitive Augmentation): Tự động phân loại nhãn và định tuyến ticket hỗ trợ, kèm theo đề xuất câu trả lời mẫu dưới dạng bản nháp nội bộ cho tổng đài viên.
+2. Khoảng trống thực tế (Reality Gaps):
+Hoàn toàn thiếu bằng chứng về việc thực thi hành động tự động (Autonomous Actions), thiếu quy trình chuyển cấp có kiểm soát (Escalation Framework) cho các ca phức tạp, và không có dữ liệu kiểm định về tỷ lệ ảo giác, tỷ lệ lỗi xử lý hoặc phản ứng khi người dùng giận dữ.
+3. Rủi ro triển khai (Deployment Risks):
+Khẳng định 'tự động hóa toàn bộ' là chiêu bài quảng cáo quá đà (AI Marketing Overpromise). Nếu công ty giao toàn quyền tự động trả lời cho khách hàng, các lỗi trả lời sai chính sách, cam kết sai thông tin tài chính hoặc giọng điệu thiếu đồng cảm sẽ phá hủy trải nghiệm khách hàng và gây khủng hoảng thương hiệu.
+4. Bài học có thể sử dụng (Actionable Lessons):
+Chỉ nên mua và tích hợp giải pháp này ở vai trò 'Trợ lý hỗ trợ nhân viên' (Copilot Mode) để tăng tốc độ phân loại và soạn thảo của tổng đài viên, tuyệt đối không bật chế độ tự hành hoàn toàn (Auto-pilot).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: 'Caveat Emptor' trong kỷ nguyên AI. Người làm sản phẩm phải biết lột bỏ lớp vỏ tiếp thị 'Full Automation' để soi chiếu vào các bằng chứng kỹ thuật thực tế. Giữ vai trò con người trong vòng lặp (Human-in-the-loop) là nguyên tắc an toàn sống còn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Cagan, M. (2017). Inspired (https://www.svpg.com/books/inspired/); Davenport, T., &amp; Ronanki, R. (2018). Artificial Intelligence for the Real World. Harvard Business Review (https://hbr.org/2018/01/artificial-intelligence-for-the-real-world)</t>
         </is>
       </c>
     </row>
@@ -1465,10 +1597,24 @@
       <c r="K23" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Viết mỗi bước theo mẫu người thực hiện → đầu vào → công cụ/hành động → đầu ra.
-Phân tích theo nguyên lý thiết kế: Viết mỗi bước theo mẫu người thực hiện → đầu vào → công cụ/hành động → đầu ra.</t>
+- Lập sơ đồ quy trình đủ các yếu tố (1.0 điểm): Trình bày rõ các bước kèm người thực hiện, đầu vào/đầu ra, công cụ và điểm bàn giao.
+- Nhận diện điểm ma sát có bằng chứng (1.0 điểm): Nêu rõ vòng lặp trả lại ở bước 4 chiếm 11/30 đơn (36,7%).
+- Phân tích vì sao chưa thể kết luận nút thắt (1.0 điểm): Chỉ ra thiếu số liệu thời gian từng bước và nêu điều chưa biết cần đo thêm.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Sơ đồ quy trình hiện trạng (Current Workflow Mapping):
+- Bước 1: [Khách hàng] -&gt; Đầu vào: Yêu cầu mua hàng -&gt; [Kinh doanh] nhận biểu mẫu -&gt; Đầu ra: Biểu mẫu khách hàng.
+- Bước 2: [Kinh doanh] -&gt; Đầu vào: Biểu mẫu -&gt; Công cụ: Bảng tính (Spreadsheet) -&gt; Đầu ra: Dữ liệu đơn nhập vào bảng tính.
+- Bước 3 (Điểm bàn giao 1): [Kỹ sư giải pháp] đọc bảng tính -&gt; Công cụ: ERP -&gt; Đối soát số dư tồn kho -&gt; Đầu ra: Kết quả kiểm tra tồn kho.
+- Bước 4 (Vòng lặp ma sát): Nếu thiếu hàng, [Kỹ sư giải pháp] gửi email phản hồi -&gt; [Kinh doanh] tiếp nhận email.
+- Bước 5 (Điểm bàn giao 2): [Kinh doanh] sửa đổi biểu mẫu yêu cầu -&gt; gửi lại cho Kỹ sư giải pháp.
+2. Đánh giá điểm ma sát và tính xác thực của nút thắt:
+- Điểm ma sát có bằng chứng (Empirical Friction Point): Vòng lặp chuyển giao qua lại giữa Bước 4 và Bước 5 xảy ra với tần suất cao: 11/30 yêu cầu bị trả lại (tỷ lệ lỗi vòng lặp lên tới 36,7%).
+- Đã đủ dữ liệu để gọi là nút thắt (Bottleneck) hay chưa?: CHƯA ĐỦ DỮ LIỆU. Mặc dù tỷ lệ lặp lại cao (36,7%), nhưng dữ liệu hiện tại chưa đo lường thời gian xử lý của từng bước (thời gian Kỹ sư tra ERP, thời gian email chờ phản hồi, thời gian sửa biểu mẫu). Một điểm chỉ được kết luận là nút thắt hệ thống khi nó chiếm tỷ trọng áp đảo trong tổng thời gian trễ (Lead Time) của toàn chu trình.
+3. Điều chưa biết cần thu thập thêm: Thời gian chờ phản hồi email trung bình giữa Kinh doanh và Kỹ sư; nguyên nhân vì sao khách/kinh doanh chọn hàng thiếu tồn kho (do bảng giá cũ hay không xem được tồn kho thời gian thực?).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Trong lý thuyết các điểm hạn chế (Theory of Constraints - TOC), tỷ lệ phát sinh lại công việc (Rework Rate) là dấu hiệu của ma sát, nhưng Nút thắt thực sự được định nghĩa bởi lưu lượng dòng chảy và thời gian chờ (Cycle Time / Wait Time). Cần đo lường thời gian phân đoạn trước khi vội vã đưa AI vào giải quyết.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Goldratt, E. M. (1984). The Goal: A Process of Ongoing Improvement (https://www.tocico.org/); Lean Enterprise Institute (https://www.lean.org/)</t>
         </is>
       </c>
     </row>
